--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -47,6 +47,93 @@
   </x:si>
   <x:si>
     <x:t>Défenseur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/1df834ab-c329-4c47-bcfd-8691e33757c2.JPG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/9f2bc74f-43e4-4e77-96a2-d43f4e7b2086.JPG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12321321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Poule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Joueur 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attaquant</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/2403d2d4-3a8c-4a2a-8e00-4fc077311ace.JPG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12321322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/9cb077de-1a90-43ff-bda1-3188692ce0dc.JPG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/280b69dc-7c22-4708-b239-309f708ab87e.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123213255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Specifique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jouer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nouveau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/d1fc017a-791a-403f-b5e5-c07e6cd4a002.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46547789</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Joueur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/f26fbf28-c2bc-446f-8042-f8d3052166ce.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>455555551</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -403,7 +490,7 @@
   <x:dimension ref="A1:G1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:10">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -426,7 +513,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:10">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -447,6 +534,212 @@
       </x:c>
       <x:c r="G2" s="0" t="s">
         <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:10">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:10">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:10">
+      <x:c r="A6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:10">
+      <x:c r="A7" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:10">
+      <x:c r="A8" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:10">
+      <x:c r="A9" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -61,6 +61,74 @@
     <x:t>Poule</x:t>
   </x:si>
   <x:si>
+    <x:t>Un joueur de football est un athlète complet qui combine endurance, technique et intelligence de jeu. Sur le terrain, il se déplace avec agilité, capable d’accélérations rapides et de changements de direction précis pour se démarquer de ses adversaires.
+Techniquement, il maîtrise le ballon avec aisance : contrôles précis, passes rapides et tirs puissants ou placés selon la situation. Son jeu peut varier selon son poste : un attaquant sera souvent opportuniste et rapide, cherchant à marquer, tandis qu’un milieu de terrain sera stratégique, organisant le jeu et distribuant les ballons. Un défenseur, lui, sera solide, concentré et prêt à intercepter ou bloquer les offensives adverses.
+Au-delà des qualités physiques, un bon joueur de football possède aussi une forte vision du jeu, une capacité à anticiper les actions et à travailler en équipe. Il doit faire preuve de discipline, de persévérance et d’un esprit compétitif, tout en respectant ses coéquipiers, ses adversaires et les règles du jeu.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>true</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/9cb077de-1a90-43ff-bda1-3188692ce0dc.JPG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attaquant</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/280b69dc-7c22-4708-b239-309f708ab87e.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123213255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Specifique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jouer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nouveau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/d1fc017a-791a-403f-b5e5-c07e6cd4a002.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46547789</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sadfafdadsfadsfasdfds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Joueur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/f26fbf28-c2bc-446f-8042-f8d3052166ce.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>455555551</x:t>
+  </x:si>
+  <x:si>
     <x:t>nom</x:t>
   </x:si>
   <x:si>
@@ -70,9 +138,6 @@
     <x:t>86</x:t>
   </x:si>
   <x:si>
-    <x:t>Attaquant</x:t>
-  </x:si>
-  <x:si>
     <x:t>/uploads/photos/2403d2d4-3a8c-4a2a-8e00-4fc077311ace.JPG</x:t>
   </x:si>
   <x:si>
@@ -82,61 +147,16 @@
     <x:t>CB</x:t>
   </x:si>
   <x:si>
-    <x:t>66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/9cb077de-1a90-43ff-bda1-3188692ce0dc.JPG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/280b69dc-7c22-4708-b239-309f708ab87e.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123213255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Specifique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jouer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nouveau</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/d1fc017a-791a-403f-b5e5-c07e6cd4a002.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46547789</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Joueur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/f26fbf28-c2bc-446f-8042-f8d3052166ce.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>455555551</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>asdfvcvb  3242</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Défenseeur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/2c4716e6-4c16-44fe-86fa-8c84455f9608.jpg</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -187,9 +207,13 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -490,7 +514,7 @@
   <x:dimension ref="A1:G1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:10">
+    <x:row r="1" spans="1:11">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -513,7 +537,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:10">
+    <x:row r="2" spans="1:11">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -536,7 +560,7 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:10">
+    <x:row r="3" spans="1:11">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -564,182 +588,331 @@
       <x:c r="I3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:10">
+      <x:c r="J3" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:11">
       <x:c r="A4" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
+      <x:c r="D5" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I4" s="0" t="s">
+      <x:c r="E5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:10">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="F5" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:10">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:11">
       <x:c r="A6" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="C6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="0">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:10">
-      <x:c r="A7" s="0">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="B7" s="0">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:10">
+    </x:row>
+    <x:row r="8" spans="1:11">
       <x:c r="A8" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:10">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:11">
       <x:c r="A9" s="0">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:11">
+      <x:c r="A10" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="0">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="0">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="K13" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -153,10 +153,28 @@
     <x:t>asdfvcvb  3242</x:t>
   </x:si>
   <x:si>
+    <x:t>/uploads/photos/2c4716e6-4c16-44fe-86fa-8c84455f9608.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
     <x:t>Défenseeur</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/photos/2c4716e6-4c16-44fe-86fa-8c84455f9608.jpg</x:t>
+    <x:t>sdfsdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fsdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dsf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/70a29da7-24a2-4167-87f5-c5d475ef2623.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>433243</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -815,7 +833,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>20</x:v>
@@ -827,10 +845,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>41</x:v>
@@ -842,7 +860,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -862,10 +880,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>41</x:v>
@@ -912,6 +930,76 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="0">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -102,54 +102,57 @@
     <x:t>Nouveau</x:t>
   </x:si>
   <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/d1fc017a-791a-403f-b5e5-c07e6cd4a002.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46547789</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sadfafdadsfadsfasdfds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Joueur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/f26fbf28-c2bc-446f-8042-f8d3052166ce.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>455555551</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Joueur 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/2403d2d4-3a8c-4a2a-8e00-4fc077311ace.JPG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12321322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CB</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>45</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/photos/d1fc017a-791a-403f-b5e5-c07e6cd4a002.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46547789</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sadfafdadsfadsfasdfds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Joueur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/f26fbf28-c2bc-446f-8042-f8d3052166ce.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>455555551</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Joueur 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/2403d2d4-3a8c-4a2a-8e00-4fc077311ace.JPG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12321322</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CB</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>asdfvcvb  3242</x:t>
   </x:si>
   <x:si>
@@ -175,6 +178,9 @@
   </x:si>
   <x:si>
     <x:t>433243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -532,7 +538,7 @@
   <x:dimension ref="A1:G1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:12">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -555,7 +561,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:11">
+    <x:row r="2" spans="1:12">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -578,7 +584,7 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:11">
+    <x:row r="3" spans="1:12">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -613,7 +619,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:11">
+    <x:row r="4" spans="1:12">
       <x:c r="A4" s="0">
         <x:v>4</x:v>
       </x:c>
@@ -642,7 +648,7 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:11">
+    <x:row r="5" spans="1:12">
       <x:c r="A5" s="0">
         <x:v>5</x:v>
       </x:c>
@@ -671,7 +677,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:11">
+    <x:row r="6" spans="1:12">
       <x:c r="A6" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -702,8 +708,14 @@
       <x:c r="J6" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:11">
+      <x:c r="K6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:12">
       <x:c r="A7" s="0">
         <x:v>7</x:v>
       </x:c>
@@ -732,7 +744,7 @@
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:11">
+    <x:row r="8" spans="1:12">
       <x:c r="A8" s="0">
         <x:v>8</x:v>
       </x:c>
@@ -764,7 +776,7 @@
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:11">
+    <x:row r="9" spans="1:12">
       <x:c r="A9" s="0">
         <x:v>10</x:v>
       </x:c>
@@ -778,7 +790,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>10</x:v>
@@ -796,7 +808,7 @@
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:11">
+    <x:row r="10" spans="1:12">
       <x:c r="A10" s="0">
         <x:v>11</x:v>
       </x:c>
@@ -825,10 +837,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:11">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:12">
       <x:c r="A11" s="0">
         <x:v>12</x:v>
       </x:c>
@@ -842,13 +854,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>41</x:v>
@@ -860,10 +872,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:11">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:12">
       <x:c r="A12" s="0">
         <x:v>13</x:v>
       </x:c>
@@ -877,13 +889,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>41</x:v>
@@ -898,7 +910,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:11">
+    <x:row r="13" spans="1:12">
       <x:c r="A13" s="0">
         <x:v>14</x:v>
       </x:c>
@@ -933,7 +945,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:11">
+    <x:row r="14" spans="1:12">
       <x:c r="A14" s="0">
         <x:v>15</x:v>
       </x:c>
@@ -941,22 +953,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
         <x:v>43</x:v>
@@ -968,7 +980,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:11">
+    <x:row r="15" spans="1:12">
       <x:c r="A15" s="0">
         <x:v>16</x:v>
       </x:c>
@@ -982,7 +994,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>22</x:v>
@@ -1000,7 +1012,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -129,6 +129,12 @@
     <x:t>455555551</x:t>
   </x:si>
   <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
     <x:t>nom</x:t>
   </x:si>
   <x:si>
@@ -147,9 +153,6 @@
     <x:t>CB</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>45</x:t>
   </x:si>
   <x:si>
@@ -157,9 +160,6 @@
   </x:si>
   <x:si>
     <x:t>/uploads/photos/2c4716e6-4c16-44fe-86fa-8c84455f9608.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
   </x:si>
   <x:si>
     <x:t>Défenseeur</x:t>
@@ -743,6 +743,15 @@
       <x:c r="I7" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0">
@@ -752,28 +761,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
@@ -790,7 +799,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>10</x:v>
@@ -837,7 +846,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
@@ -854,25 +863,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
@@ -889,22 +898,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>16</x:v>
@@ -959,7 +968,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>51</x:v>
@@ -971,10 +980,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
         <x:v>16</x:v>
@@ -1009,13 +1018,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -132,34 +132,34 @@
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>nom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Joueur 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/2403d2d4-3a8c-4a2a-8e00-4fc077311ace.JPG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12321322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdfvcvb  3242</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/photos/2c4716e6-4c16-44fe-86fa-8c84455f9608.jpg</x:t>
+  </x:si>
+  <x:si>
     <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Joueur 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/2403d2d4-3a8c-4a2a-8e00-4fc077311ace.JPG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12321322</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdfvcvb  3242</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/2c4716e6-4c16-44fe-86fa-8c84455f9608.jpg</x:t>
   </x:si>
   <x:si>
     <x:t>Défenseeur</x:t>
@@ -761,25 +761,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
+      <x:c r="I8" s="0" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>37</x:v>
@@ -799,7 +799,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>10</x:v>
@@ -846,7 +846,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
@@ -863,16 +863,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>31</x:v>
@@ -881,7 +881,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
@@ -898,16 +898,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>31</x:v>
@@ -968,7 +968,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>51</x:v>
@@ -1021,10 +1021,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -163,21 +163,6 @@
   </x:si>
   <x:si>
     <x:t>Défenseeur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdfsdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fsdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dsf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/70a29da7-24a2-4167-87f5-c5d475ef2623.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>433243</x:t>
   </x:si>
   <x:si>
     <x:t>22</x:t>
@@ -956,74 +941,39 @@
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" s="0">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:12">
-      <x:c r="A15" s="0">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B15" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L15" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -52,31 +52,67 @@
     <x:t>Actif</x:t>
   </x:si>
   <x:si>
+    <x:t>CleUnique</x:t>
+  </x:si>
+  <x:si>
     <x:t>Bélisle</x:t>
   </x:si>
   <x:si>
     <x:t>Samuel</x:t>
   </x:si>
   <x:si>
-    <x:t>62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/bf0a62d3-68a0-4c1d-a047-65368b1291f5.JPG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>815043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attaque|Centre,Défense|Defensive Tackle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Samuel a commencé son parcours au avec les Rhinos.</x:t>
+    <x:t>135487</x:t>
+  </x:si>
+  <x:si>
+    <x:t>014e46d8-90ab-4f67-bce8-f680643173a6</x:t>
   </x:si>
   <x:si>
     <x:t>true</x:t>
   </x:si>
   <x:si>
-    <x:t>D&amp;amp;#xE9;fense</x:t>
+    <x:t>Corrivea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4654654</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19332178-bc78-4584-917b-ee996be03662</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEst</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41635465</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e94ef335-12b6-461d-9305-8d96f65aac0b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>eistein</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albert</x:t>
+  </x:si>
+  <x:si>
+    <x:t>414564</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e15e9204-87e2-4ce3-94b6-3ddbe9db46e8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>3410d9a8-da29-4d29-ae2d-60035b23f93d</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -427,10 +463,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L1"/>
+  <x:dimension ref="A1:M1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:12">
+    <x:row r="1" spans="1:13">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -467,8 +503,11 @@
       <x:c r="L1" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="M1" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:12">
+    <x:row r="2" spans="1:13">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -476,34 +515,123 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:13">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>19</x:v>
+      <x:c r="F3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:13">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:13">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:13">
+      <x:c r="A6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/joueurs.xlsx
+++ b/Data/joueurs.xlsx
@@ -19,7 +19,7 @@
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>EquipeId</x:t>
+    <x:t>EcoleId</x:t>
   </x:si>
   <x:si>
     <x:t>Nom</x:t>
@@ -28,22 +28,10 @@
     <x:t>Prenom</x:t>
   </x:si>
   <x:si>
-    <x:t>Numero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Position</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PhotoPath</x:t>
-  </x:si>
-  <x:si>
     <x:t>NoFiche</x:t>
   </x:si>
   <x:si>
-    <x:t>PositionSpecifique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
+    <x:t>CleUnique</x:t>
   </x:si>
   <x:si>
     <x:t>ConsentementPhoto</x:t>
@@ -52,67 +40,28 @@
     <x:t>Actif</x:t>
   </x:si>
   <x:si>
-    <x:t>CleUnique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bélisle</x:t>
+    <x:t>Corriveau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brian</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>4d75db6c-f8e5-4dce-a777-2715ed461c03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>true</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Contant</x:t>
   </x:si>
   <x:si>
     <x:t>Samuel</x:t>
   </x:si>
   <x:si>
-    <x:t>135487</x:t>
-  </x:si>
-  <x:si>
-    <x:t>014e46d8-90ab-4f67-bce8-f680643173a6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>true</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corrivea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4654654</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19332178-bc78-4584-917b-ee996be03662</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEst</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41635465</x:t>
-  </x:si>
-  <x:si>
-    <x:t>e94ef335-12b6-461d-9305-8d96f65aac0b</x:t>
-  </x:si>
-  <x:si>
-    <x:t>eistein</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Albert</x:t>
-  </x:si>
-  <x:si>
-    <x:t>414564</x:t>
-  </x:si>
-  <x:si>
-    <x:t>e15e9204-87e2-4ce3-94b6-3ddbe9db46e8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>3410d9a8-da29-4d29-ae2d-60035b23f93d</x:t>
+    <x:t>c1d21d1d-81b8-49f8-8d11-97c76318f494</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -463,10 +412,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M1"/>
+  <x:dimension ref="A1:H1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:13">
+    <x:row r="1" spans="1:8">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -491,23 +440,8 @@
       <x:c r="H1" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I1" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K1" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L1" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M1" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
     </x:row>
-    <x:row r="2" spans="1:13">
+    <x:row r="2" spans="1:8">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -515,25 +449,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:13">
+    <x:row r="3" spans="1:8">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -541,97 +475,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:13">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:13">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:13">
-      <x:c r="A6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
